--- a/data/trans_camb/P16A06-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A06-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,93</t>
+          <t>-0,66; 1,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 2,6</t>
+          <t>-0,12; 2,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 7,76</t>
+          <t>3,38; 7,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,18</t>
+          <t>1,42; 5,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,53; 9,34</t>
+          <t>4,65; 9,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,55; 12,46</t>
+          <t>8,53; 12,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,12</t>
+          <t>0,74; 3,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,49</t>
+          <t>2,81; 5,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,68; 9,61</t>
+          <t>6,67; 9,51</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-46,57; 270,85</t>
+          <t>-40,88; 265,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 373,67</t>
+          <t>-14,96; 378,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>173,35; 1127,48</t>
+          <t>167,03; 1042,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62,74; 482,24</t>
+          <t>49,54; 533,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>175,86; 846,63</t>
+          <t>169,0; 869,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>316,38; 1292,11</t>
+          <t>311,8; 1223,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,69; 317,45</t>
+          <t>38,81; 292,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>139,85; 553,3</t>
+          <t>139,65; 564,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>331,26; 957,98</t>
+          <t>327,01; 1016,06</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,44</t>
+          <t>-1,71; 0,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 2,18</t>
+          <t>-0,46; 2,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 2,81</t>
+          <t>-0,65; 2,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,51</t>
+          <t>2,24; 6,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,4</t>
+          <t>0,49; 4,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,26; 7,95</t>
+          <t>4,35; 8,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,09</t>
+          <t>0,57; 3,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,69</t>
+          <t>0,41; 2,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,69</t>
+          <t>1,37; 4,74</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-73,12; 51,16</t>
+          <t>-73,47; 51,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,56; 217,63</t>
+          <t>-23,9; 198,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 252,35</t>
+          <t>-18,75; 248,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50,86; 263,8</t>
+          <t>51,87; 272,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,83; 189,04</t>
+          <t>9,09; 167,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,1; 342,93</t>
+          <t>98,94; 334,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,08; 149,14</t>
+          <t>15,97; 153,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,62; 134,03</t>
+          <t>13,89; 137,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50,61; 229,25</t>
+          <t>49,38; 232,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,52</t>
+          <t>-1,11; 2,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 2,15</t>
+          <t>-0,98; 2,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,68</t>
+          <t>1,15; 4,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 2,46</t>
+          <t>-2,55; 2,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,95</t>
+          <t>-0,92; 4,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 4,44</t>
+          <t>-2,67; 4,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,78</t>
+          <t>-1,3; 1,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 2,59</t>
+          <t>-0,4; 2,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,1</t>
+          <t>0,08; 4,02</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-44,89; 211,74</t>
+          <t>-46,19; 227,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,52; 208,44</t>
+          <t>-41,72; 187,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,01; 434,4</t>
+          <t>34,6; 452,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-39,08; 58,47</t>
+          <t>-40,33; 56,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 92,58</t>
+          <t>-13,69; 98,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,01; 93,93</t>
+          <t>-40,29; 96,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-28,98; 58,27</t>
+          <t>-30,18; 53,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 89,84</t>
+          <t>-8,84; 88,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,99; 140,79</t>
+          <t>3,18; 127,07</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,76</t>
+          <t>-1,53; 1,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,76</t>
+          <t>-1,58; 1,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,14</t>
+          <t>1,56; 5,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,81</t>
+          <t>-1,63; 2,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,87</t>
+          <t>0,96; 5,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,55; 7,84</t>
+          <t>2,39; 7,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,82</t>
+          <t>-0,81; 1,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,36</t>
+          <t>0,51; 3,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,97; 6,02</t>
+          <t>2,73; 6,08</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-43,92; 82,53</t>
+          <t>-42,09; 76,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,88; 78,4</t>
+          <t>-41,11; 73,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35,2; 221,32</t>
+          <t>35,81; 242,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 57,97</t>
+          <t>-22,95; 58,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,4; 124,59</t>
+          <t>13,25; 124,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,65; 164,29</t>
+          <t>35,24; 158,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 46,47</t>
+          <t>-16,21; 48,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,23; 91,77</t>
+          <t>10,02; 88,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>54,92; 158,44</t>
+          <t>55,88; 162,45</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,78</t>
+          <t>-0,62; 0,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 1,4</t>
+          <t>-0,13; 1,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,78</t>
+          <t>1,63; 3,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,18</t>
+          <t>1,11; 3,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,4</t>
+          <t>2,26; 4,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,04</t>
+          <t>3,72; 6,93</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,78</t>
+          <t>0,47; 1,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,83</t>
+          <t>1,39; 2,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,13</t>
+          <t>3,13; 5,08</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 44,9</t>
+          <t>-27,0; 47,12</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 86,63</t>
+          <t>-5,36; 82,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>79,08; 229,36</t>
+          <t>70,91; 227,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23,92; 85,08</t>
+          <t>23,87; 87,31</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>45,74; 117,74</t>
+          <t>48,25; 119,9</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,77; 192,54</t>
+          <t>85,29; 189,49</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,93; 65,96</t>
+          <t>14,49; 63,92</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>40,08; 100,38</t>
+          <t>40,5; 99,83</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>99,65; 185,41</t>
+          <t>97,33; 179,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A06-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A06-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,39</t>
+          <t>5,26</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,55</t>
+          <t>10,38</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8,06</t>
+          <t>7,9</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,89</t>
+          <t>-0,69; 1,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 2,8</t>
+          <t>-0,18; 2,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 7,49</t>
+          <t>3,31; 7,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,14</t>
+          <t>1,52; 5,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,65; 9,52</t>
+          <t>4,54; 9,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,53; 12,57</t>
+          <t>8,09; 12,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,01</t>
+          <t>0,75; 3,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 5,47</t>
+          <t>2,76; 5,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,67; 9,51</t>
+          <t>6,58; 9,43</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>434,42%</t>
+          <t>423,33%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>630,61%</t>
+          <t>620,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>553,27%</t>
+          <t>542,45%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,88; 265,98</t>
+          <t>-46,59; 259,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 378,81</t>
+          <t>-21,37; 376,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>167,03; 1042,94</t>
+          <t>131,17; 977,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49,54; 533,72</t>
+          <t>55,65; 489,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>169,0; 869,67</t>
+          <t>189,27; 879,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>311,8; 1223,68</t>
+          <t>309,63; 1279,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,81; 292,34</t>
+          <t>37,02; 297,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>139,65; 564,07</t>
+          <t>134,15; 514,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>327,01; 1016,06</t>
+          <t>320,0; 921,86</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,2</t>
+          <t>5,99</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,39</t>
+          <t>4,1</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 0,43</t>
+          <t>-1,73; 0,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 2,2</t>
+          <t>-0,37; 2,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,83</t>
+          <t>0,72; 3,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,53</t>
+          <t>2,18; 6,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,26</t>
+          <t>0,55; 4,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 8,06</t>
+          <t>4,25; 8,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,07</t>
+          <t>0,82; 3,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,71</t>
+          <t>0,48; 2,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,74</t>
+          <t>2,93; 5,29</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>130,71%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>187,69%</t>
+          <t>181,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>136,6%</t>
+          <t>165,12%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-73,47; 51,81</t>
+          <t>-72,37; 59,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,9; 198,0</t>
+          <t>-20,93; 227,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 248,95</t>
+          <t>22,33; 351,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,87; 272,84</t>
+          <t>48,82; 268,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,09; 167,95</t>
+          <t>11,56; 179,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,94; 334,85</t>
+          <t>92,2; 333,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,97; 153,44</t>
+          <t>26,79; 153,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,89; 137,78</t>
+          <t>14,02; 137,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49,38; 232,58</t>
+          <t>92,0; 264,14</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,88</t>
+          <t>3,08</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>3,47</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>3,27</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,43</t>
+          <t>-1,03; 2,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,04</t>
+          <t>-1,02; 2,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,7</t>
+          <t>1,27; 5,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,49</t>
+          <t>-2,58; 2,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 4,14</t>
+          <t>-1,13; 4,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 4,6</t>
+          <t>1,01; 6,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,66</t>
+          <t>-1,17; 1,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 2,57</t>
+          <t>-0,58; 2,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 4,02</t>
+          <t>1,79; 4,74</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>155,81%</t>
+          <t>166,31%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>88,96%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-46,19; 227,0</t>
+          <t>-44,94; 217,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,72; 187,34</t>
+          <t>-42,03; 191,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34,6; 452,82</t>
+          <t>30,61; 413,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,33; 56,33</t>
+          <t>-39,48; 49,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 98,91</t>
+          <t>-20,91; 93,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,29; 96,35</t>
+          <t>15,13; 148,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,18; 53,12</t>
+          <t>-27,75; 60,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 88,57</t>
+          <t>-13,47; 83,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,18; 127,07</t>
+          <t>38,95; 156,83</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,2</t>
+          <t>2,84</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,27</t>
+          <t>5,62</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>4,33</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 1,64</t>
+          <t>-1,4; 1,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,66</t>
+          <t>-1,24; 1,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,26</t>
+          <t>1,2; 4,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 2,81</t>
+          <t>-1,4; 2,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,84</t>
+          <t>0,7; 5,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,58</t>
+          <t>3,36; 7,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,76</t>
+          <t>-1,01; 1,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,36</t>
+          <t>0,39; 3,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,08</t>
+          <t>3,1; 5,82</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>108,38%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,09; 76,99</t>
+          <t>-39,5; 70,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,11; 73,74</t>
+          <t>-35,74; 72,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35,81; 242,2</t>
+          <t>29,03; 202,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 58,97</t>
+          <t>-21,2; 55,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,25; 124,21</t>
+          <t>9,7; 115,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,24; 158,81</t>
+          <t>46,71; 156,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 48,66</t>
+          <t>-19,17; 47,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,02; 88,22</t>
+          <t>7,56; 90,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>55,88; 162,45</t>
+          <t>61,32; 160,75</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,87</t>
+          <t>3,17</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,68</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,33</t>
+          <t>4,75</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,74</t>
+          <t>-0,73; 0,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,41</t>
+          <t>-0,05; 1,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,78</t>
+          <t>2,35; 4,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,25</t>
+          <t>1,04; 3,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,51</t>
+          <t>2,31; 4,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,93</t>
+          <t>5,14; 7,3</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,79</t>
+          <t>0,48; 1,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,75</t>
+          <t>1,38; 2,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,08</t>
+          <t>4,07; 5,49</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>144,77%</t>
+          <t>159,7%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>136,4%</t>
+          <t>149,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>140,04%</t>
+          <t>153,61%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-27,0; 47,12</t>
+          <t>-31,25; 45,28</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 82,98</t>
+          <t>-2,85; 85,92</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>70,91; 227,68</t>
+          <t>97,49; 239,76</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23,87; 87,31</t>
+          <t>21,14; 85,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>48,25; 119,9</t>
+          <t>49,66; 120,93</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,29; 189,49</t>
+          <t>108,94; 202,2</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,49; 63,92</t>
+          <t>13,58; 64,33</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>40,5; 99,83</t>
+          <t>40,86; 100,99</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>97,33; 179,57</t>
+          <t>117,5; 197,17</t>
         </is>
       </c>
     </row>
